--- a/Firmware/Modules/Fault/Fault_State_Machine.xlsx
+++ b/Firmware/Modules/Fault/Fault_State_Machine.xlsx
@@ -10,6 +10,7 @@
     <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="۱ بیت‌ها" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="۲ آشکارسازها" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="۳ خطای فنی" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -55,7 +56,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -75,11 +76,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E2F3"/>
       </patternFill>
     </fill>
     <fill>
@@ -140,13 +136,13 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -155,10 +151,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -527,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -594,72 +590,89 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr"/>
-      <c r="B5" s="4" t="inlineStr"/>
-      <c r="C5" s="4" t="inlineStr"/>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>۳ خطای فنی</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Fault فقط بیت مرکزی سناریوی ۷ را منتشر می‌کند؛ تشخیص و قفل با Charger است</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>app_types.h، charger.c، task_control.c</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>رنگ‌ها</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr"/>
+      <c r="A6" s="4" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
+          <t>رنگ‌ها</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
           <t>فایل‌های مرجع</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Firmware/Modules/Fault/fault.c، Firmware/Config/Inc/app_types.h</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>tools/make_module_state_machines.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>برگهٔ اعتبارسنجی همین ماژول</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Fault_Validation.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
+          <t>برگهٔ اعتبارسنجی همین ماژول</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Fault_Validation.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
           <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
@@ -670,8 +683,8 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -684,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -914,6 +927,33 @@
       <c r="E9" s="9" t="inlineStr">
         <is>
           <t>چهرهٔ «قطع باتری» در UI و توقف شارژ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>۷</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>FAULT_CHARGER_TECHNICAL</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Charger امضای رله باز + PWM صفر + JIT یا PWM &gt;۲۰٪ + جریان صفر را ست می‌کند</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>فقط reset/power-cycle؛ مالک RAM latch، نه تنظیمات پنل</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>UI سناریوی ۷</t>
         </is>
       </c>
     </row>
@@ -1117,4 +1157,123 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002F5597"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>نقش Fault در سناریوی ۷ — انتشار بیت مرکزی و پاک‌شدن فقط با reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>بخش</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>شرط</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>رفتار</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>مرجع</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>بیت مرکزی</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Charger امضای فنی را دید</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>FAULT_CHARGER_TECHNICAL (bit 7) ست می‌شود</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>app_types.h</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>مالک تشخیص</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>snapshot معتبر</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Fault تشخیص نمی‌دهد؛ task_control پس از Charger بیت را refresh می‌کند</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>task_control.c</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>پاک‌سازی</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>reset/power-cycle</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Fault_Init بیت RAM را پاک می‌کند؛ تنظیم پنل یا NVM کافی نیست</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>fault.c / charger.c</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Firmware/Modules/Fault/Fault_State_Machine.xlsx
+++ b/Firmware/Modules/Fault/Fault_State_Machine.xlsx
@@ -70,7 +70,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F5597"/>
+        <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
     <fill>
@@ -519,7 +519,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -693,7 +693,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -968,7 +968,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1162,7 +1162,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>

--- a/Firmware/Modules/Fault/Fault_State_Machine.xlsx
+++ b/Firmware/Modules/Fault/Fault_State_Machine.xlsx
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>نیمی زیر حد نبودِ باتری (۲۹) با ورودی در بازهٔ ۳۳..۳۴</t>
+          <t>نیمی زیر حد نبودِ باتری (۲۹) با مجوز مشترک ورودی Fault (۳۳/۳۴ + ۱۶۹/۱۷۰)</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">

--- a/Firmware/Modules/Fault/Fault_State_Machine.xlsx
+++ b/Firmware/Modules/Fault/Fault_State_Machine.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="۱ بیت‌ها" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="۲ آشکارسازها" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="۳ خطای فنی" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="۱ بیت‌ها" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="۲ آشکارسازها" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="۳ خطای فنی" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
